--- a/Documents/SmartEdu_Requirements.xlsx
+++ b/Documents/SmartEdu_Requirements.xlsx
@@ -1,572 +1,594 @@
 
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
-  <si>
-    <t xml:space="preserve">Req ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feature Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requirement Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acceptance Criteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Authentication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System shall authenticate users via email and password using Firebase Authentication.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All Users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRS 3.1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login succeeds with valid credentials within 3 seconds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System shall allow user registration and automatically assign a role (Student/Teacher).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New user can register and see role-appropriate dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System shall provide a Forgot Password feature that sends a reset link to the user's email.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Password reset email is received and functional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Users shall be able to update personal information (name, phone, bio).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profile changes are saved and displayed immediately</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Users shall be able to upload a profile picture via Cloudinary.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profile picture is uploaded and displayed in profile view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teachers shall be able to create a new course with title, description, schedule, and emoji.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teacher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRS 3.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New course appears in teacher's dashboard after creation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teachers shall be able to upload course materials (documents, links, notes) to a course.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uploaded material appears in course detail content list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teachers shall be able to upload lecture videos to a course via Cloudinary.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uploaded video appears in lessons list and is playable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Students shall be able to view all their enrolled courses on a dashboard.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student dashboard shows all enrolled courses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teachers shall be able to approve or reject student enrollment requests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pending badge updates after approval/rejection action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teachers shall be able to assign homework (Assignment) with deadline and file attachment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assignment appears in course detail for enrolled students</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Students shall be able to submit homework files for an assignment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submission is recorded and visible to teacher for grading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teachers shall be able to create an exam with title, time limit, passing score, and deadline.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRS 3.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exam appears in exam management list after creation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teachers shall be able to import exam questions from an Excel (.xlsx) file.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questions from Excel file appear in exam question list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Students shall be able to take an exam within the allocated time limit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exam auto-submits when timer reaches zero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System shall auto-grade multiple-choice exams upon submission.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student/System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score is calculated and stored correctly after submission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teachers shall be able to edit exam questions before the exam is published.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changes to questions are saved and reflected in exam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System shall generate individual exam reports detailing student score and answer review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student/Teacher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRS 3.4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exam report shows correct/incorrect answers per question</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teacher dashboard shall display aggregated statistics (average score, pass rate) per course.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dashboard stats update after each new submission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System shall send in-app notifications to students for new exams, grades, and materials.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notification bell shows correct unread count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin shall be able to create, activate, and close academic semesters.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRS 3.5.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semester status change reflected for all users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin shall be able to view a centralized dashboard of system activity and user roles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin dashboard loads without errors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin shall be able to block or unblock user accounts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blocked user is forced to log out within 15 seconds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verification Method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90% of new users shall be able to complete their first login without external assistance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRS 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User testing with first-time users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All key exam actions (answer, navigate, submit) shall be operable with keyboard alone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual keyboard-only navigation test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Performance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The system shall support at least 50 concurrent users without response degradation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load testing simulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% of REST API responses shall be received within 3 seconds under normal load.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API latency monitoring over 1-week period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI screens shall render within 2 seconds after navigation on a standard laptop.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stopwatch measurement on reference hardware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All network communications shall use HTTPS with TLS 1.2 or higher.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network traffic inspection with Wireshark / Fiddler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User passwords shall never be stored in plaintext on the client device (handled by Firebase).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Code review of authentication flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JWT tokens shall expire after a configurable session period and require re-authentication.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automated session timeout test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Availability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The backend Azure API shall maintain at least 99% uptime during exam periods.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure Monitor uptime dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The system shall be available 24/7 except for scheduled maintenance windows communicated in advance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintenance log review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robustness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If the client loses internet during an exam, the student's selected answers shall be auto-saved locally and synced upon reconnection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual test: disconnect/reconnect during active exam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The application shall display a user-friendly error message for all unhandled exceptions without crashing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error injection testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintainability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The codebase shall follow a layered architecture (Models, DTOs, Services, Views) for separation of concerns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architecture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Code review and folder structure inspection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFR-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scalability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The system architecture shall support adding new user roles without major refactoring.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRS 2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architecture design review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feature (Backlog)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRS Section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Objective</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Case ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">BO-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BR-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BR-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BO-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BO-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BR-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BR-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BR-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BR-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEAT-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BR-6</t>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dinhq\source\repos\SE104_E-learningSystem\Documents\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1462D1D-114C-4E2E-915F-C47AC0DC4247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Functional Requirements" sheetId="1" r:id="rId1"/>
+    <sheet name="Non-Functional Requirements" sheetId="2" r:id="rId2"/>
+    <sheet name="Traceability Matrix" sheetId="3" r:id="rId3"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="183">
+  <si>
+    <t>Req ID</t>
+  </si>
+  <si>
+    <t>Feature Area</t>
+  </si>
+  <si>
+    <t>Requirement Description</t>
+  </si>
+  <si>
+    <t>User Role</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Acceptance Criteria</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>FR-01</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>System shall authenticate users via email and password using Firebase Authentication.</t>
+  </si>
+  <si>
+    <t>All Users</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>SRS 3.1.2</t>
+  </si>
+  <si>
+    <t>Login succeeds with valid credentials within 3 seconds</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>FR-02</t>
+  </si>
+  <si>
+    <t>System shall allow user registration and automatically assign a role (Student/Teacher).</t>
+  </si>
+  <si>
+    <t>New user can register and see role-appropriate dashboard</t>
+  </si>
+  <si>
+    <t>FR-03</t>
+  </si>
+  <si>
+    <t>System shall provide a Forgot Password feature that sends a reset link to the user's email.</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Password reset email is received and functional</t>
+  </si>
+  <si>
+    <t>FR-04</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>Users shall be able to update personal information (name, phone, bio).</t>
+  </si>
+  <si>
+    <t>Profile changes are saved and displayed immediately</t>
+  </si>
+  <si>
+    <t>FR-05</t>
+  </si>
+  <si>
+    <t>Users shall be able to upload a profile picture via Cloudinary.</t>
+  </si>
+  <si>
+    <t>Profile picture is uploaded and displayed in profile view</t>
+  </si>
+  <si>
+    <t>FR-06</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>Teachers shall be able to create a new course with title, description, schedule, and emoji.</t>
+  </si>
+  <si>
+    <t>Teacher</t>
+  </si>
+  <si>
+    <t>SRS 3.2.2</t>
+  </si>
+  <si>
+    <t>New course appears in teacher's dashboard after creation</t>
+  </si>
+  <si>
+    <t>FR-07</t>
+  </si>
+  <si>
+    <t>Teachers shall be able to upload course materials (documents, links, notes) to a course.</t>
+  </si>
+  <si>
+    <t>Uploaded material appears in course detail content list</t>
+  </si>
+  <si>
+    <t>FR-08</t>
+  </si>
+  <si>
+    <t>Teachers shall be able to upload lecture videos to a course via Cloudinary.</t>
+  </si>
+  <si>
+    <t>Uploaded video appears in lessons list and is playable</t>
+  </si>
+  <si>
+    <t>FR-09</t>
+  </si>
+  <si>
+    <t>Students shall be able to view all their enrolled courses on a dashboard.</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>Student dashboard shows all enrolled courses</t>
+  </si>
+  <si>
+    <t>FR-10</t>
+  </si>
+  <si>
+    <t>Teachers shall be able to approve or reject student enrollment requests.</t>
+  </si>
+  <si>
+    <t>Pending badge updates after approval/rejection action</t>
+  </si>
+  <si>
+    <t>FR-11</t>
+  </si>
+  <si>
+    <t>Teachers shall be able to assign homework (Assignment) with deadline and file attachment.</t>
+  </si>
+  <si>
+    <t>Assignment appears in course detail for enrolled students</t>
+  </si>
+  <si>
+    <t>FR-12</t>
+  </si>
+  <si>
+    <t>Students shall be able to submit homework files for an assignment.</t>
+  </si>
+  <si>
+    <t>Submission is recorded and visible to teacher for grading</t>
+  </si>
+  <si>
+    <t>FR-13</t>
+  </si>
+  <si>
+    <t>Exam</t>
+  </si>
+  <si>
+    <t>Teachers shall be able to create an exam with title, time limit, passing score, and deadline.</t>
+  </si>
+  <si>
+    <t>SRS 3.3.2</t>
+  </si>
+  <si>
+    <t>Exam appears in exam management list after creation</t>
+  </si>
+  <si>
+    <t>FR-14</t>
+  </si>
+  <si>
+    <t>Teachers shall be able to import exam questions from an Excel (.xlsx) file.</t>
+  </si>
+  <si>
+    <t>Questions from Excel file appear in exam question list</t>
+  </si>
+  <si>
+    <t>FR-15</t>
+  </si>
+  <si>
+    <t>Students shall be able to take an exam within the allocated time limit.</t>
+  </si>
+  <si>
+    <t>Exam auto-submits when timer reaches zero</t>
+  </si>
+  <si>
+    <t>FR-16</t>
+  </si>
+  <si>
+    <t>System shall auto-grade multiple-choice exams upon submission.</t>
+  </si>
+  <si>
+    <t>Student/System</t>
+  </si>
+  <si>
+    <t>Score is calculated and stored correctly after submission</t>
+  </si>
+  <si>
+    <t>FR-17</t>
+  </si>
+  <si>
+    <t>Teachers shall be able to edit exam questions before the exam is published.</t>
+  </si>
+  <si>
+    <t>Changes to questions are saved and reflected in exam</t>
+  </si>
+  <si>
+    <t>FR-18</t>
+  </si>
+  <si>
+    <t>Report</t>
+  </si>
+  <si>
+    <t>System shall generate individual exam reports detailing student score and answer review.</t>
+  </si>
+  <si>
+    <t>Student/Teacher</t>
+  </si>
+  <si>
+    <t>SRS 3.4.2</t>
+  </si>
+  <si>
+    <t>Exam report shows correct/incorrect answers per question</t>
+  </si>
+  <si>
+    <t>FR-19</t>
+  </si>
+  <si>
+    <t>Teacher dashboard shall display aggregated statistics (average score, pass rate) per course.</t>
+  </si>
+  <si>
+    <t>Dashboard stats update after each new submission</t>
+  </si>
+  <si>
+    <t>FR-20</t>
+  </si>
+  <si>
+    <t>Notification</t>
+  </si>
+  <si>
+    <t>System shall send in-app notifications to students for new exams, grades, and materials.</t>
+  </si>
+  <si>
+    <t>Notification bell shows correct unread count</t>
+  </si>
+  <si>
+    <t>FR-21</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Admin shall be able to create, activate, and close academic semesters.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>SRS 3.5.2</t>
+  </si>
+  <si>
+    <t>Semester status change reflected for all users</t>
+  </si>
+  <si>
+    <t>FR-22</t>
+  </si>
+  <si>
+    <t>Admin shall be able to view a centralized dashboard of system activity and user roles.</t>
+  </si>
+  <si>
+    <t>Admin dashboard loads without errors</t>
+  </si>
+  <si>
+    <t>FR-23</t>
+  </si>
+  <si>
+    <t>Admin shall be able to block or unblock user accounts.</t>
+  </si>
+  <si>
+    <t>Blocked user is forced to log out within 15 seconds</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Verification Method</t>
+  </si>
+  <si>
+    <t>NFR-01</t>
+  </si>
+  <si>
+    <t>Usability</t>
+  </si>
+  <si>
+    <t>90% of new users shall be able to complete their first login without external assistance.</t>
+  </si>
+  <si>
+    <t>SRS 6</t>
+  </si>
+  <si>
+    <t>User testing with first-time users</t>
+  </si>
+  <si>
+    <t>NFR-02</t>
+  </si>
+  <si>
+    <t>All key exam actions (answer, navigate, submit) shall be operable with keyboard alone.</t>
+  </si>
+  <si>
+    <t>Manual keyboard-only navigation test</t>
+  </si>
+  <si>
+    <t>NFR-03</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>The system shall support at least 50 concurrent users without response degradation.</t>
+  </si>
+  <si>
+    <t>Load testing simulation</t>
+  </si>
+  <si>
+    <t>NFR-04</t>
+  </si>
+  <si>
+    <t>95% of REST API responses shall be received within 3 seconds under normal load.</t>
+  </si>
+  <si>
+    <t>API latency monitoring over 1-week period</t>
+  </si>
+  <si>
+    <t>NFR-05</t>
+  </si>
+  <si>
+    <t>UI screens shall render within 2 seconds after navigation on a standard laptop.</t>
+  </si>
+  <si>
+    <t>Stopwatch measurement on reference hardware</t>
+  </si>
+  <si>
+    <t>NFR-06</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>All network communications shall use HTTPS with TLS 1.2 or higher.</t>
+  </si>
+  <si>
+    <t>Network traffic inspection with Wireshark / Fiddler</t>
+  </si>
+  <si>
+    <t>NFR-07</t>
+  </si>
+  <si>
+    <t>User passwords shall never be stored in plaintext on the client device (handled by Firebase).</t>
+  </si>
+  <si>
+    <t>Code review of authentication flow</t>
+  </si>
+  <si>
+    <t>NFR-08</t>
+  </si>
+  <si>
+    <t>JWT tokens shall expire after a configurable session period and require re-authentication.</t>
+  </si>
+  <si>
+    <t>Automated session timeout test</t>
+  </si>
+  <si>
+    <t>NFR-09</t>
+  </si>
+  <si>
+    <t>Availability</t>
+  </si>
+  <si>
+    <t>The backend Azure API shall maintain at least 99% uptime during exam periods.</t>
+  </si>
+  <si>
+    <t>Azure Monitor uptime dashboard</t>
+  </si>
+  <si>
+    <t>NFR-10</t>
+  </si>
+  <si>
+    <t>The system shall be available 24/7 except for scheduled maintenance windows communicated in advance.</t>
+  </si>
+  <si>
+    <t>Maintenance log review</t>
+  </si>
+  <si>
+    <t>NFR-11</t>
+  </si>
+  <si>
+    <t>Robustness</t>
+  </si>
+  <si>
+    <t>If the client loses internet during an exam, the student's selected answers shall be auto-saved locally and synced upon reconnection.</t>
+  </si>
+  <si>
+    <t>Manual test: disconnect/reconnect during active exam</t>
+  </si>
+  <si>
+    <t>NFR-12</t>
+  </si>
+  <si>
+    <t>The application shall display a user-friendly error message for all unhandled exceptions without crashing.</t>
+  </si>
+  <si>
+    <t>Error injection testing</t>
+  </si>
+  <si>
+    <t>NFR-13</t>
+  </si>
+  <si>
+    <t>Maintainability</t>
+  </si>
+  <si>
+    <t>The codebase shall follow a layered architecture (Models, DTOs, Services, Views) for separation of concerns.</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>Code review and folder structure inspection</t>
+  </si>
+  <si>
+    <t>NFR-14</t>
+  </si>
+  <si>
+    <t>Scalability</t>
+  </si>
+  <si>
+    <t>The system architecture shall support adding new user roles without major refactoring.</t>
+  </si>
+  <si>
+    <t>SRS 2.4</t>
+  </si>
+  <si>
+    <t>Architecture design review</t>
+  </si>
+  <si>
+    <t>Feature (Backlog)</t>
+  </si>
+  <si>
+    <t>SRS Section</t>
+  </si>
+  <si>
+    <t>Business Rule</t>
+  </si>
+  <si>
+    <t>Business Objective</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>FEAT-01</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>BO-2</t>
+  </si>
+  <si>
+    <t>FEAT-02</t>
+  </si>
+  <si>
+    <t>FEAT-03</t>
+  </si>
+  <si>
+    <t>BR-8</t>
+  </si>
+  <si>
+    <t>FEAT-04</t>
+  </si>
+  <si>
+    <t>FEAT-05</t>
+  </si>
+  <si>
+    <t>BR-2</t>
+  </si>
+  <si>
+    <t>BO-1</t>
+  </si>
+  <si>
+    <t>BO-3</t>
+  </si>
+  <si>
+    <t>FEAT-06</t>
+  </si>
+  <si>
+    <t>FEAT-08</t>
+  </si>
+  <si>
+    <t>FEAT-09</t>
+  </si>
+  <si>
+    <t>BR-4</t>
+  </si>
+  <si>
+    <t>FEAT-11</t>
+  </si>
+  <si>
+    <t>BR-7</t>
+  </si>
+  <si>
+    <t>FEAT-10</t>
+  </si>
+  <si>
+    <t>FEAT-12</t>
+  </si>
+  <si>
+    <t>BR-5</t>
+  </si>
+  <si>
+    <t>FEAT-13</t>
+  </si>
+  <si>
+    <t>FEAT-16</t>
+  </si>
+  <si>
+    <t>FEAT-14</t>
+  </si>
+  <si>
+    <t>BR-1</t>
+  </si>
+  <si>
+    <t>FEAT-15</t>
+  </si>
+  <si>
+    <t>BR-6</t>
   </si>
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <b/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills>
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -579,7 +601,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -591,55 +613,382 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheets>
-    <sheet name="Functional Requirements" sheetId="1" r:id="rId1"/>
-    <sheet name="Non-Functional Requirements" sheetId="2" r:id="rId2"/>
-    <sheet name="Traceability Matrix" sheetId="3" r:id="rId3"/>
-  </sheets>
-</workbook>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
 </file>
 
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" customWidth="1"/>
+    <col min="6" max="6" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
+    <row r="1" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -665,7 +1014,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -691,7 +1040,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -717,7 +1066,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -743,7 +1092,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -769,7 +1118,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -795,7 +1144,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -821,7 +1170,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -847,7 +1196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -873,7 +1222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -899,7 +1248,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -925,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -951,7 +1300,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -977,7 +1326,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -1003,7 +1352,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -1029,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -1055,7 +1404,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>70</v>
       </c>
@@ -1081,7 +1430,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>73</v>
       </c>
@@ -1107,7 +1456,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -1133,7 +1482,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>82</v>
       </c>
@@ -1159,7 +1508,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>86</v>
       </c>
@@ -1185,7 +1534,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>92</v>
       </c>
@@ -1211,7 +1560,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>95</v>
       </c>
@@ -1238,33 +1587,36 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
+    <row r="1" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="B1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="F1" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -1284,7 +1636,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>105</v>
       </c>
@@ -1304,7 +1656,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>108</v>
       </c>
@@ -1324,7 +1676,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>112</v>
       </c>
@@ -1344,7 +1696,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>115</v>
       </c>
@@ -1364,7 +1716,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>118</v>
       </c>
@@ -1384,7 +1736,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>122</v>
       </c>
@@ -1404,7 +1756,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -1424,7 +1776,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>128</v>
       </c>
@@ -1444,7 +1796,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>132</v>
       </c>
@@ -1464,7 +1816,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -1484,7 +1836,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>139</v>
       </c>
@@ -1504,7 +1856,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>142</v>
       </c>
@@ -1524,7 +1876,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>147</v>
       </c>
@@ -1545,33 +1897,36 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
+    <row r="1" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="B1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="C1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="D1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="E1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="F1" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1591,7 +1946,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1611,7 +1966,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1631,7 +1986,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1651,7 +2006,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1671,7 +2026,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1691,7 +2046,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -1711,7 +2066,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -1731,7 +2086,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -1751,7 +2106,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -1771,7 +2126,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -1791,7 +2146,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -1811,7 +2166,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -1831,7 +2186,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -1851,7 +2206,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -1871,7 +2226,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -1891,7 +2246,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>70</v>
       </c>
@@ -1911,7 +2266,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>73</v>
       </c>
@@ -1931,7 +2286,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -1951,7 +2306,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>82</v>
       </c>
@@ -1971,7 +2326,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>86</v>
       </c>
@@ -1991,7 +2346,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>92</v>
       </c>
@@ -2011,7 +2366,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>95</v>
       </c>
@@ -2031,7 +2386,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>100</v>
       </c>
@@ -2051,7 +2406,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>108</v>
       </c>
@@ -2071,7 +2426,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -2091,7 +2446,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>122</v>
       </c>
@@ -2111,7 +2466,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>135</v>
       </c>
@@ -2131,7 +2486,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>128</v>
       </c>
@@ -2152,5 +2507,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>